--- a/analysis/Analysis2/L_2_Vasilkov.xlsx
+++ b/analysis/Analysis2/L_2_Vasilkov.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0895640-8BA7-4DC6-9560-0E0F77B939FB}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
@@ -30,7 +29,7 @@
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">6</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
@@ -42,7 +41,7 @@
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -69,7 +68,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -262,25 +261,19 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>15241</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>624840</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>166259</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>607263</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>87528</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D929270-1701-4CD7-B5AE-91B6C1235765}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="4" name="Рисунок 3"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -293,37 +286,12 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="525780" y="1798321"/>
-          <a:ext cx="2026920" cy="516778"/>
+          <a:off x="502920" y="2194560"/>
+          <a:ext cx="3457143" cy="819048"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln w="22225">
-          <a:gradFill flip="none" rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="67000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="48000">
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="97000"/>
-                  <a:lumOff val="3000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="16200000" scaled="1"/>
-            <a:tileRect/>
-          </a:gradFill>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -593,7 +561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B5:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -614,14 +582,14 @@
     </row>
     <row r="6" spans="2:4" ht="18" x14ac:dyDescent="0.35">
       <c r="B6" s="9">
-        <v>0</v>
+        <v>0.28571428571428575</v>
       </c>
       <c r="C6" s="10">
-        <v>2</v>
+        <v>0.64285714285714302</v>
       </c>
       <c r="D6" s="4">
-        <f>2*B6*C6 - POWER(B6, 2) - 2* POWER(C6, 2)</f>
-        <v>-8</v>
+        <f xml:space="preserve"> 2*POWER(B6, 2)+ POWER(C6, 2)  - B6-B6*C6</f>
+        <v>0.10714285714285729</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.35">
@@ -635,8 +603,8 @@
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
-        <f>2*B6+3*C6</f>
-        <v>6</v>
+        <f>(-1)*B6+2*C6</f>
+        <v>1.0000000000000002</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
